--- a/artfynd/A 22913-2024 artfynd.xlsx
+++ b/artfynd/A 22913-2024 artfynd.xlsx
@@ -10908,10 +10908,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118041350</v>
+        <v>118041056</v>
       </c>
       <c r="B88" t="n">
-        <v>57534</v>
+        <v>90902</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10920,39 +10920,34 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103012</v>
+        <v>5420</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10960,13 +10955,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>587766</v>
+        <v>587638</v>
       </c>
       <c r="R88" t="n">
-        <v>6312294</v>
+        <v>6312281</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11004,6 +10999,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -11141,10 +11137,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118041110</v>
+        <v>118041441</v>
       </c>
       <c r="B90" t="n">
-        <v>57303</v>
+        <v>97836</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11153,35 +11149,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11189,10 +11193,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>587640</v>
+        <v>587384</v>
       </c>
       <c r="R90" t="n">
-        <v>6312259</v>
+        <v>6312195</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11233,6 +11237,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11251,10 +11256,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118041441</v>
+        <v>118041110</v>
       </c>
       <c r="B91" t="n">
-        <v>97836</v>
+        <v>57303</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11263,43 +11268,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -11307,10 +11304,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>587384</v>
+        <v>587640</v>
       </c>
       <c r="R91" t="n">
-        <v>6312195</v>
+        <v>6312259</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11351,7 +11348,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11370,10 +11366,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118041056</v>
+        <v>118041350</v>
       </c>
       <c r="B92" t="n">
-        <v>90902</v>
+        <v>57534</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11382,34 +11378,39 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5420</v>
+        <v>103012</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11417,13 +11418,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>587638</v>
+        <v>587766</v>
       </c>
       <c r="R92" t="n">
-        <v>6312281</v>
+        <v>6312294</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11461,7 +11462,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11480,7 +11480,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118041187</v>
+        <v>118040936</v>
       </c>
       <c r="B93" t="n">
         <v>57440</v>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -11532,13 +11532,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>587340</v>
+        <v>587845</v>
       </c>
       <c r="R93" t="n">
-        <v>6312205</v>
+        <v>6312295</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118040936</v>
+        <v>118041187</v>
       </c>
       <c r="B95" t="n">
         <v>57440</v>
@@ -11743,7 +11743,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -11760,13 +11760,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>587845</v>
+        <v>587340</v>
       </c>
       <c r="R95" t="n">
-        <v>6312295</v>
+        <v>6312205</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>

--- a/artfynd/A 22913-2024 artfynd.xlsx
+++ b/artfynd/A 22913-2024 artfynd.xlsx
@@ -10908,10 +10908,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118041056</v>
+        <v>118040858</v>
       </c>
       <c r="B88" t="n">
-        <v>90902</v>
+        <v>97838</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10920,34 +10920,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10955,10 +10964,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>587638</v>
+        <v>587920</v>
       </c>
       <c r="R88" t="n">
-        <v>6312281</v>
+        <v>6312343</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11018,10 +11027,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118040858</v>
+        <v>118040936</v>
       </c>
       <c r="B89" t="n">
-        <v>97836</v>
+        <v>57441</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11030,43 +11039,39 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -11074,13 +11079,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>587920</v>
+        <v>587845</v>
       </c>
       <c r="R89" t="n">
-        <v>6312343</v>
+        <v>6312295</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11118,7 +11123,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -11140,7 +11144,7 @@
         <v>118041441</v>
       </c>
       <c r="B90" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11259,7 +11263,7 @@
         <v>118041110</v>
       </c>
       <c r="B91" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11369,7 +11373,7 @@
         <v>118041350</v>
       </c>
       <c r="B92" t="n">
-        <v>57534</v>
+        <v>57535</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11480,10 +11484,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118040936</v>
+        <v>118041019</v>
       </c>
       <c r="B93" t="n">
-        <v>57440</v>
+        <v>57304</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11496,33 +11500,33 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -11532,13 +11536,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>587845</v>
+        <v>587664</v>
       </c>
       <c r="R93" t="n">
-        <v>6312295</v>
+        <v>6312271</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11594,10 +11598,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118041019</v>
+        <v>118041056</v>
       </c>
       <c r="B94" t="n">
-        <v>57303</v>
+        <v>90904</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11606,39 +11610,34 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11646,10 +11645,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>587664</v>
+        <v>587638</v>
       </c>
       <c r="R94" t="n">
-        <v>6312271</v>
+        <v>6312281</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11690,6 +11689,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11708,10 +11708,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118041187</v>
+        <v>118041087</v>
       </c>
       <c r="B95" t="n">
-        <v>57440</v>
+        <v>57304</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11724,33 +11724,29 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -11760,13 +11756,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>587340</v>
+        <v>587645</v>
       </c>
       <c r="R95" t="n">
-        <v>6312205</v>
+        <v>6312263</v>
       </c>
       <c r="S95" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11822,10 +11818,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118041087</v>
+        <v>118041187</v>
       </c>
       <c r="B96" t="n">
-        <v>57303</v>
+        <v>57441</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11838,29 +11834,33 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -11870,13 +11870,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>587645</v>
+        <v>587340</v>
       </c>
       <c r="R96" t="n">
-        <v>6312263</v>
+        <v>6312205</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>

--- a/artfynd/A 22913-2024 artfynd.xlsx
+++ b/artfynd/A 22913-2024 artfynd.xlsx
@@ -11935,7 +11935,7 @@
         <v>122254462</v>
       </c>
       <c r="B97" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>

--- a/artfynd/A 22913-2024 artfynd.xlsx
+++ b/artfynd/A 22913-2024 artfynd.xlsx
@@ -11950,11 +11950,6 @@
       <c r="E97" t="n">
         <v>205998</v>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>

--- a/artfynd/A 22913-2024 artfynd.xlsx
+++ b/artfynd/A 22913-2024 artfynd.xlsx
@@ -11935,7 +11935,7 @@
         <v>122254462</v>
       </c>
       <c r="B97" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11949,6 +11949,11 @@
       </c>
       <c r="E97" t="n">
         <v>205998</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>

--- a/artfynd/A 22913-2024 artfynd.xlsx
+++ b/artfynd/A 22913-2024 artfynd.xlsx
@@ -11935,7 +11935,7 @@
         <v>122254462</v>
       </c>
       <c r="B97" t="n">
-        <v>56275</v>
+        <v>56276</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>

--- a/artfynd/A 22913-2024 artfynd.xlsx
+++ b/artfynd/A 22913-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY97"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3140,7 +3140,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112300630</v>
+        <v>112300930</v>
       </c>
       <c r="B22" t="n">
         <v>96783</v>
@@ -3175,17 +3175,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587799</v>
+        <v>587756</v>
       </c>
       <c r="R22" t="n">
-        <v>6312439</v>
+        <v>6312230</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3259,7 +3259,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112300930</v>
+        <v>112300469</v>
       </c>
       <c r="B23" t="n">
         <v>96783</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587756</v>
+        <v>587850</v>
       </c>
       <c r="R23" t="n">
-        <v>6312230</v>
+        <v>6312497</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3378,7 +3378,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112300469</v>
+        <v>112301041</v>
       </c>
       <c r="B24" t="n">
         <v>96783</v>
@@ -3413,17 +3413,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587850</v>
+        <v>587988</v>
       </c>
       <c r="R24" t="n">
-        <v>6312497</v>
+        <v>6312301</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112301041</v>
+        <v>112301016</v>
       </c>
       <c r="B25" t="n">
         <v>96783</v>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587988</v>
+        <v>587871</v>
       </c>
       <c r="R25" t="n">
-        <v>6312301</v>
+        <v>6312247</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112301016</v>
+        <v>112300922</v>
       </c>
       <c r="B26" t="n">
-        <v>96783</v>
+        <v>90210</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3628,43 +3628,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3672,10 +3667,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587871</v>
+        <v>587744</v>
       </c>
       <c r="R26" t="n">
-        <v>6312247</v>
+        <v>6312233</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3735,10 +3730,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112300383</v>
+        <v>112301033</v>
       </c>
       <c r="B27" t="n">
-        <v>96783</v>
+        <v>89991</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3747,43 +3742,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3791,10 +3781,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587936</v>
+        <v>587955</v>
       </c>
       <c r="R27" t="n">
-        <v>6312441</v>
+        <v>6312278</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3854,10 +3844,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112300922</v>
+        <v>112300773</v>
       </c>
       <c r="B28" t="n">
-        <v>90210</v>
+        <v>96783</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3866,38 +3856,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3905,10 +3900,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587744</v>
+        <v>587688</v>
       </c>
       <c r="R28" t="n">
-        <v>6312233</v>
+        <v>6312367</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3968,10 +3963,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112301033</v>
+        <v>112300794</v>
       </c>
       <c r="B29" t="n">
-        <v>89991</v>
+        <v>96783</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3980,38 +3975,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587955</v>
+        <v>587705</v>
       </c>
       <c r="R29" t="n">
-        <v>6312278</v>
+        <v>6312289</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112300773</v>
+        <v>112300281</v>
       </c>
       <c r="B30" t="n">
         <v>96783</v>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587688</v>
+        <v>587997</v>
       </c>
       <c r="R30" t="n">
-        <v>6312367</v>
+        <v>6312332</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112300794</v>
+        <v>112300759</v>
       </c>
       <c r="B31" t="n">
         <v>96783</v>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587705</v>
+        <v>587698</v>
       </c>
       <c r="R31" t="n">
-        <v>6312289</v>
+        <v>6312428</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4320,7 +4320,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112300281</v>
+        <v>112300980</v>
       </c>
       <c r="B32" t="n">
         <v>96783</v>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587997</v>
+        <v>587792</v>
       </c>
       <c r="R32" t="n">
-        <v>6312332</v>
+        <v>6312274</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4439,7 +4439,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112300759</v>
+        <v>112300266</v>
       </c>
       <c r="B33" t="n">
         <v>96783</v>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587698</v>
+        <v>588002</v>
       </c>
       <c r="R33" t="n">
-        <v>6312428</v>
+        <v>6312321</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4558,7 +4558,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112300980</v>
+        <v>112300330</v>
       </c>
       <c r="B34" t="n">
         <v>96783</v>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587792</v>
+        <v>587968</v>
       </c>
       <c r="R34" t="n">
-        <v>6312274</v>
+        <v>6312394</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112300266</v>
+        <v>112300991</v>
       </c>
       <c r="B35" t="n">
         <v>96783</v>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588002</v>
+        <v>587837</v>
       </c>
       <c r="R35" t="n">
-        <v>6312321</v>
+        <v>6312229</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4796,7 +4796,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112300330</v>
+        <v>112300459</v>
       </c>
       <c r="B36" t="n">
         <v>96783</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587968</v>
+        <v>587853</v>
       </c>
       <c r="R36" t="n">
-        <v>6312394</v>
+        <v>6312502</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4915,7 +4915,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112300991</v>
+        <v>112300617</v>
       </c>
       <c r="B37" t="n">
         <v>96783</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4971,10 +4971,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587837</v>
+        <v>587818</v>
       </c>
       <c r="R37" t="n">
-        <v>6312229</v>
+        <v>6312474</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -5034,7 +5034,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112300459</v>
+        <v>112300871</v>
       </c>
       <c r="B38" t="n">
         <v>96783</v>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587853</v>
+        <v>587737</v>
       </c>
       <c r="R38" t="n">
-        <v>6312502</v>
+        <v>6312268</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5153,7 +5153,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112300617</v>
+        <v>112335058</v>
       </c>
       <c r="B39" t="n">
         <v>96783</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587818</v>
+        <v>587743</v>
       </c>
       <c r="R39" t="n">
-        <v>6312474</v>
+        <v>6312387</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5239,12 +5239,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5272,7 +5272,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112300871</v>
+        <v>112335069</v>
       </c>
       <c r="B40" t="n">
         <v>96783</v>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587737</v>
+        <v>587732</v>
       </c>
       <c r="R40" t="n">
-        <v>6312268</v>
+        <v>6312375</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5358,12 +5358,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5391,7 +5391,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112335058</v>
+        <v>112335129</v>
       </c>
       <c r="B41" t="n">
         <v>96783</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587743</v>
+        <v>587605</v>
       </c>
       <c r="R41" t="n">
-        <v>6312387</v>
+        <v>6312307</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5510,7 +5510,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112335069</v>
+        <v>112335176</v>
       </c>
       <c r="B42" t="n">
         <v>96783</v>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587732</v>
+        <v>587540</v>
       </c>
       <c r="R42" t="n">
-        <v>6312375</v>
+        <v>6312284</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5629,7 +5629,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112335129</v>
+        <v>112334986</v>
       </c>
       <c r="B43" t="n">
         <v>96783</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5685,10 +5685,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587605</v>
+        <v>587813</v>
       </c>
       <c r="R43" t="n">
-        <v>6312307</v>
+        <v>6312312</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5748,7 +5748,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112335176</v>
+        <v>112335112</v>
       </c>
       <c r="B44" t="n">
         <v>96783</v>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587540</v>
+        <v>587611</v>
       </c>
       <c r="R44" t="n">
-        <v>6312284</v>
+        <v>6312335</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5867,7 +5867,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112334986</v>
+        <v>112334607</v>
       </c>
       <c r="B45" t="n">
         <v>96783</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587813</v>
+        <v>587632</v>
       </c>
       <c r="R45" t="n">
-        <v>6312312</v>
+        <v>6312252</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5986,7 +5986,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112335112</v>
+        <v>112335008</v>
       </c>
       <c r="B46" t="n">
         <v>96783</v>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587611</v>
+        <v>587849</v>
       </c>
       <c r="R46" t="n">
-        <v>6312335</v>
+        <v>6312304</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6105,7 +6105,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112334607</v>
+        <v>112334797</v>
       </c>
       <c r="B47" t="n">
         <v>96783</v>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587632</v>
+        <v>587731</v>
       </c>
       <c r="R47" t="n">
-        <v>6312252</v>
+        <v>6312272</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6224,7 +6224,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112335008</v>
+        <v>112334680</v>
       </c>
       <c r="B48" t="n">
         <v>96783</v>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587849</v>
+        <v>587669</v>
       </c>
       <c r="R48" t="n">
-        <v>6312304</v>
+        <v>6312246</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6343,7 +6343,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112334797</v>
+        <v>112334559</v>
       </c>
       <c r="B49" t="n">
         <v>96783</v>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>587731</v>
+        <v>587565</v>
       </c>
       <c r="R49" t="n">
-        <v>6312272</v>
+        <v>6312279</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6462,7 +6462,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112334680</v>
+        <v>112335193</v>
       </c>
       <c r="B50" t="n">
         <v>96783</v>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6518,10 +6518,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>587669</v>
+        <v>587618</v>
       </c>
       <c r="R50" t="n">
-        <v>6312246</v>
+        <v>6312216</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6581,7 +6581,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112334559</v>
+        <v>112334692</v>
       </c>
       <c r="B51" t="n">
         <v>96783</v>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6637,10 +6637,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587565</v>
+        <v>587655</v>
       </c>
       <c r="R51" t="n">
-        <v>6312279</v>
+        <v>6312283</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6700,7 +6700,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112335193</v>
+        <v>112335029</v>
       </c>
       <c r="B52" t="n">
         <v>96783</v>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6756,10 +6756,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587618</v>
+        <v>587805</v>
       </c>
       <c r="R52" t="n">
-        <v>6312216</v>
+        <v>6312407</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6819,10 +6819,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112334692</v>
+        <v>112334542</v>
       </c>
       <c r="B53" t="n">
-        <v>96783</v>
+        <v>90210</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6831,43 +6831,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6875,10 +6870,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>587655</v>
+        <v>587568</v>
       </c>
       <c r="R53" t="n">
-        <v>6312283</v>
+        <v>6312279</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6938,7 +6933,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112335029</v>
+        <v>112334976</v>
       </c>
       <c r="B54" t="n">
         <v>96783</v>
@@ -6973,7 +6968,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6994,10 +6989,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>587805</v>
+        <v>587789</v>
       </c>
       <c r="R54" t="n">
-        <v>6312407</v>
+        <v>6312319</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -7057,10 +7052,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112334542</v>
+        <v>112334714</v>
       </c>
       <c r="B55" t="n">
-        <v>90210</v>
+        <v>96783</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7069,38 +7064,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7108,10 +7108,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>587568</v>
+        <v>587712</v>
       </c>
       <c r="R55" t="n">
-        <v>6312279</v>
+        <v>6312265</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7171,10 +7171,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112334976</v>
+        <v>112577312</v>
       </c>
       <c r="B56" t="n">
-        <v>96783</v>
+        <v>96996</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7204,36 +7204,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Strömsrum 2:1, Sm</t>
+          <t>ålem, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587789</v>
+        <v>587644</v>
       </c>
       <c r="R56" t="n">
-        <v>6312319</v>
+        <v>6312326</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7257,12 +7245,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7278,22 +7266,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112334714</v>
+        <v>112577123</v>
       </c>
       <c r="B57" t="n">
-        <v>96783</v>
+        <v>104055</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7302,57 +7290,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Strömsrum 2:1, Sm</t>
+          <t>Ålem, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>587712</v>
+        <v>588005</v>
       </c>
       <c r="R57" t="n">
-        <v>6312265</v>
+        <v>6312341</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7376,12 +7356,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7397,19 +7377,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112577312</v>
+        <v>112577298</v>
       </c>
       <c r="B58" t="n">
         <v>96996</v>
@@ -7449,14 +7429,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>ålem, Sm</t>
+          <t>Ålem, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>587644</v>
+        <v>587723</v>
       </c>
       <c r="R58" t="n">
-        <v>6312326</v>
+        <v>6312379</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7516,10 +7496,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112577123</v>
+        <v>112577405</v>
       </c>
       <c r="B59" t="n">
-        <v>104055</v>
+        <v>96996</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7528,46 +7508,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ålem, Sm</t>
+          <t>ålem, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>588005</v>
+        <v>587805</v>
       </c>
       <c r="R59" t="n">
-        <v>6312341</v>
+        <v>6312317</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7627,7 +7603,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112577298</v>
+        <v>112577282</v>
       </c>
       <c r="B60" t="n">
         <v>96996</v>
@@ -7671,10 +7647,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>587723</v>
+        <v>587749</v>
       </c>
       <c r="R60" t="n">
-        <v>6312379</v>
+        <v>6312387</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7734,7 +7710,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112577405</v>
+        <v>112577389</v>
       </c>
       <c r="B61" t="n">
         <v>96996</v>
@@ -7781,7 +7757,7 @@
         <v>587805</v>
       </c>
       <c r="R61" t="n">
-        <v>6312317</v>
+        <v>6312320</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7841,7 +7817,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112577282</v>
+        <v>112577371</v>
       </c>
       <c r="B62" t="n">
         <v>96996</v>
@@ -7881,14 +7857,14 @@
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ålem, Sm</t>
+          <t>ålem, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>587749</v>
+        <v>587792</v>
       </c>
       <c r="R62" t="n">
-        <v>6312387</v>
+        <v>6312307</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7948,7 +7924,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112577389</v>
+        <v>112577243</v>
       </c>
       <c r="B63" t="n">
         <v>96996</v>
@@ -7988,14 +7964,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>ålem, Sm</t>
+          <t>Ålem, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>587805</v>
+        <v>587841</v>
       </c>
       <c r="R63" t="n">
-        <v>6312320</v>
+        <v>6312474</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8055,7 +8031,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112577371</v>
+        <v>112585100</v>
       </c>
       <c r="B64" t="n">
         <v>96996</v>
@@ -8088,24 +8064,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>ålem, Sm</t>
+          <t>Strömsrum 2:1, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>587792</v>
+        <v>587980</v>
       </c>
       <c r="R64" t="n">
-        <v>6312307</v>
+        <v>6312325</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8150,22 +8138,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112577243</v>
+        <v>112585004</v>
       </c>
       <c r="B65" t="n">
-        <v>96996</v>
+        <v>89735</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8174,45 +8162,52 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ålem, Sm</t>
+          <t>Strömsrum 2:1, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>587841</v>
+        <v>587601</v>
       </c>
       <c r="R65" t="n">
-        <v>6312474</v>
+        <v>6312282</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8257,19 +8252,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112585100</v>
+        <v>112585068</v>
       </c>
       <c r="B66" t="n">
         <v>96996</v>
@@ -8304,7 +8299,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8325,10 +8320,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>587980</v>
+        <v>587710</v>
       </c>
       <c r="R66" t="n">
-        <v>6312325</v>
+        <v>6312410</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8388,10 +8383,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112585004</v>
+        <v>112584739</v>
       </c>
       <c r="B67" t="n">
-        <v>89735</v>
+        <v>96996</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8400,38 +8395,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>587601</v>
+        <v>587801</v>
       </c>
       <c r="R67" t="n">
-        <v>6312282</v>
+        <v>6312278</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8502,7 +8502,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112585068</v>
+        <v>112584628</v>
       </c>
       <c r="B68" t="n">
         <v>96996</v>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>587710</v>
+        <v>587846</v>
       </c>
       <c r="R68" t="n">
-        <v>6312410</v>
+        <v>6312443</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8621,7 +8621,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112584739</v>
+        <v>112584669</v>
       </c>
       <c r="B69" t="n">
         <v>96996</v>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8677,10 +8677,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>587801</v>
+        <v>587910</v>
       </c>
       <c r="R69" t="n">
-        <v>6312278</v>
+        <v>6312319</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8740,7 +8740,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112584628</v>
+        <v>112584614</v>
       </c>
       <c r="B70" t="n">
         <v>96996</v>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8792,14 +8792,14 @@
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Strömsrum 2:1, Sm</t>
+          <t>Torp 4.6, Sm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>587846</v>
+        <v>587880</v>
       </c>
       <c r="R70" t="n">
-        <v>6312443</v>
+        <v>6312425</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8859,7 +8859,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112584669</v>
+        <v>112585045</v>
       </c>
       <c r="B71" t="n">
         <v>96996</v>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8915,10 +8915,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>587910</v>
+        <v>587572</v>
       </c>
       <c r="R71" t="n">
-        <v>6312319</v>
+        <v>6312265</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8978,7 +8978,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112584614</v>
+        <v>112585092</v>
       </c>
       <c r="B72" t="n">
         <v>96996</v>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9030,14 +9030,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torp 4.6, Sm</t>
+          <t>Strömsrum 2:1, Sm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>587880</v>
+        <v>587668</v>
       </c>
       <c r="R72" t="n">
-        <v>6312425</v>
+        <v>6312388</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9097,7 +9097,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>112585045</v>
+        <v>112584639</v>
       </c>
       <c r="B73" t="n">
         <v>96996</v>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>587572</v>
+        <v>587825</v>
       </c>
       <c r="R73" t="n">
-        <v>6312265</v>
+        <v>6312310</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9216,10 +9216,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112585092</v>
+        <v>112585022</v>
       </c>
       <c r="B74" t="n">
-        <v>96996</v>
+        <v>90387</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9228,43 +9228,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9272,10 +9267,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>587668</v>
+        <v>587585</v>
       </c>
       <c r="R74" t="n">
-        <v>6312388</v>
+        <v>6312281</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9335,7 +9330,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>112584639</v>
+        <v>112584664</v>
       </c>
       <c r="B75" t="n">
         <v>96996</v>
@@ -9370,7 +9365,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9391,10 +9386,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>587825</v>
+        <v>587932</v>
       </c>
       <c r="R75" t="n">
-        <v>6312310</v>
+        <v>6312327</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9454,10 +9449,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>112585022</v>
+        <v>112584967</v>
       </c>
       <c r="B76" t="n">
-        <v>90387</v>
+        <v>96996</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9466,38 +9461,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>587585</v>
+        <v>587635</v>
       </c>
       <c r="R76" t="n">
-        <v>6312281</v>
+        <v>6312316</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9568,7 +9568,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112584664</v>
+        <v>112584654</v>
       </c>
       <c r="B77" t="n">
         <v>96996</v>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>587932</v>
+        <v>587873</v>
       </c>
       <c r="R77" t="n">
-        <v>6312327</v>
+        <v>6312315</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9687,7 +9687,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>112584967</v>
+        <v>112584774</v>
       </c>
       <c r="B78" t="n">
         <v>96996</v>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>587635</v>
+        <v>587742</v>
       </c>
       <c r="R78" t="n">
-        <v>6312316</v>
+        <v>6312250</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9806,10 +9806,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>112584654</v>
+        <v>112695354</v>
       </c>
       <c r="B79" t="n">
-        <v>96996</v>
+        <v>97021</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9841,31 +9841,23 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Strömsrum 2:1, Sm</t>
+          <t>Nooreskog, Strömsrum, Sm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>587873</v>
+        <v>587642</v>
       </c>
       <c r="R79" t="n">
-        <v>6312315</v>
+        <v>6312256</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9895,9 +9887,19 @@
           <t>2023-10-07</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9913,22 +9915,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112584774</v>
+        <v>112695346</v>
       </c>
       <c r="B80" t="n">
-        <v>96996</v>
+        <v>97021</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9960,31 +9962,23 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Strömsrum 2:1, Sm</t>
+          <t>Norreskog, Strömsrum, Sm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>587742</v>
+        <v>587667</v>
       </c>
       <c r="R80" t="n">
-        <v>6312250</v>
+        <v>6312227</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10014,9 +10008,19 @@
           <t>2023-10-07</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10032,22 +10036,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112695354</v>
+        <v>112695374</v>
       </c>
       <c r="B81" t="n">
-        <v>97021</v>
+        <v>57281</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10056,46 +10060,50 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nooreskog, Strömsrum, Sm</t>
+          <t>Norreskog, Strömsrum, Sm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>587642</v>
+        <v>587639</v>
       </c>
       <c r="R81" t="n">
-        <v>6312256</v>
+        <v>6312241</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10146,7 +10154,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10165,7 +10172,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112695346</v>
+        <v>112695382</v>
       </c>
       <c r="B82" t="n">
         <v>97021</v>
@@ -10200,7 +10207,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J82" t="inlineStr"/>
@@ -10213,10 +10220,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>587667</v>
+        <v>587638</v>
       </c>
       <c r="R82" t="n">
-        <v>6312227</v>
+        <v>6312300</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10286,10 +10293,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112695374</v>
+        <v>112695366</v>
       </c>
       <c r="B83" t="n">
-        <v>57281</v>
+        <v>97021</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10298,39 +10305,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10338,10 +10341,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>587639</v>
+        <v>587677</v>
       </c>
       <c r="R83" t="n">
-        <v>6312241</v>
+        <v>6312280</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10392,6 +10395,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10410,7 +10414,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112695382</v>
+        <v>112695338</v>
       </c>
       <c r="B84" t="n">
         <v>97021</v>
@@ -10445,7 +10449,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J84" t="inlineStr"/>
@@ -10458,10 +10462,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>587638</v>
+        <v>587682</v>
       </c>
       <c r="R84" t="n">
-        <v>6312300</v>
+        <v>6312233</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10531,10 +10535,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112695366</v>
+        <v>114306796</v>
       </c>
       <c r="B85" t="n">
-        <v>97021</v>
+        <v>56181</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10543,49 +10547,55 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100111</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norreskog, Strömsrum, Sm</t>
+          <t>Strömsrum, Sm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>587677</v>
+        <v>587413</v>
       </c>
       <c r="R85" t="n">
-        <v>6312280</v>
+        <v>6312150</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10609,22 +10619,27 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>01:18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>01:19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>. Calluna AB. .</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10633,29 +10648,32 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Marielle Gustafsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112695338</v>
+        <v>118041056</v>
       </c>
       <c r="B86" t="n">
-        <v>97021</v>
+        <v>90908</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10664,49 +10682,48 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norreskog, Strömsrum, Sm</t>
+          <t>Strömsrum 2:1, Sm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>587682</v>
+        <v>587638</v>
       </c>
       <c r="R86" t="n">
-        <v>6312233</v>
+        <v>6312281</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10730,22 +10747,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10761,22 +10768,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>114306796</v>
+        <v>118041187</v>
       </c>
       <c r="B87" t="n">
-        <v>56181</v>
+        <v>57443</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10785,25 +10792,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100111</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -10811,29 +10818,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Strömsrum, Sm</t>
+          <t>Strömsrum 2:1, Sm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>587413</v>
+        <v>587340</v>
       </c>
       <c r="R87" t="n">
-        <v>6312150</v>
+        <v>6312205</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10857,27 +10862,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>01:18</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>01:19</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>. Calluna AB. .</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10892,26 +10882,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>André Dabolins</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118041056</v>
+        <v>118041110</v>
       </c>
       <c r="B88" t="n">
-        <v>90908</v>
+        <v>57306</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10920,34 +10906,35 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10955,10 +10942,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>587638</v>
+        <v>587640</v>
       </c>
       <c r="R88" t="n">
-        <v>6312281</v>
+        <v>6312259</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10999,7 +10986,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -11018,10 +11004,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118041187</v>
+        <v>118041019</v>
       </c>
       <c r="B89" t="n">
-        <v>57443</v>
+        <v>57306</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11034,21 +11020,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -11060,7 +11046,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -11070,13 +11056,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>587340</v>
+        <v>587664</v>
       </c>
       <c r="R89" t="n">
-        <v>6312205</v>
+        <v>6312271</v>
       </c>
       <c r="S89" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11132,10 +11118,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118041110</v>
+        <v>118040936</v>
       </c>
       <c r="B90" t="n">
-        <v>57306</v>
+        <v>57443</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11148,29 +11134,33 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -11180,13 +11170,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>587640</v>
+        <v>587845</v>
       </c>
       <c r="R90" t="n">
-        <v>6312259</v>
+        <v>6312295</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11242,10 +11232,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118041019</v>
+        <v>118040858</v>
       </c>
       <c r="B91" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11254,39 +11244,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -11294,10 +11288,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>587664</v>
+        <v>587920</v>
       </c>
       <c r="R91" t="n">
-        <v>6312271</v>
+        <v>6312343</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11338,6 +11332,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11356,10 +11351,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118040936</v>
+        <v>118041441</v>
       </c>
       <c r="B92" t="n">
-        <v>57443</v>
+        <v>97846</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11368,39 +11363,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11408,13 +11407,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>587845</v>
+        <v>587384</v>
       </c>
       <c r="R92" t="n">
-        <v>6312295</v>
+        <v>6312195</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11452,6 +11451,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11470,10 +11470,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118040858</v>
+        <v>118041087</v>
       </c>
       <c r="B93" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11482,43 +11482,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11526,10 +11518,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>587920</v>
+        <v>587645</v>
       </c>
       <c r="R93" t="n">
-        <v>6312343</v>
+        <v>6312263</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11570,7 +11562,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11589,10 +11580,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118041441</v>
+        <v>118041350</v>
       </c>
       <c r="B94" t="n">
-        <v>97846</v>
+        <v>57537</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11601,43 +11592,39 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>103012</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11645,13 +11632,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>587384</v>
+        <v>587766</v>
       </c>
       <c r="R94" t="n">
-        <v>6312195</v>
+        <v>6312294</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11689,7 +11676,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11708,10 +11694,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118041087</v>
+        <v>122254462</v>
       </c>
       <c r="B95" t="n">
-        <v>57306</v>
+        <v>56276</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11724,45 +11710,51 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>205998</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Strömsrum 2:1, Sm</t>
+          <t>Strömsrum, Sm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>587645</v>
+        <v>587627</v>
       </c>
       <c r="R95" t="n">
-        <v>6312263</v>
+        <v>6312195</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11786,12 +11778,27 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>00:13</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>00:14</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11803,272 +11810,27 @@
       <c r="AG95" t="b">
         <v>0</v>
       </c>
-      <c r="AT95" t="inlineStr"/>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Marielle Gustafsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>118041350</v>
-      </c>
-      <c r="B96" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>103012</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Grönsångare</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Phylloscopus sibilatrix</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Strömsrum 2:1, Sm</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>587766</v>
-      </c>
-      <c r="R96" t="n">
-        <v>6312294</v>
-      </c>
-      <c r="S96" t="n">
-        <v>50</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Ålem</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Lars Engström</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Lars Engström</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>122254462</v>
-      </c>
-      <c r="B97" t="n">
-        <v>56276</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Eptesicus nilssonii</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Strömsrum, Sm</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>587627</v>
-      </c>
-      <c r="R97" t="n">
-        <v>6312195</v>
-      </c>
-      <c r="S97" t="n">
-        <v>5</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Ålem</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>00:13</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>00:14</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS97" t="inlineStr">
-        <is>
           <t>André Dabolins</t>
         </is>
       </c>
-      <c r="AT97" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Marielle Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>André Dabolins</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr">
+      <c r="AY95" t="inlineStr">
         <is>
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
